--- a/docs/Mapping_casi_uso/cittadinanza/Citt_025.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_025.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="142">
   <si>
     <t>Sezione</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>flag dichiarante</t>
@@ -490,11 +496,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.73828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.0546875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -1407,7 +1413,7 @@
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>38</v>
@@ -1470,19 +1476,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1493,16 +1499,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>103</v>
@@ -1516,7 +1522,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>104</v>
@@ -1525,7 +1531,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>105</v>
@@ -1539,7 +1545,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>106</v>
@@ -1548,7 +1554,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>107</v>
@@ -1562,7 +1568,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>108</v>
@@ -1571,7 +1577,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>109</v>
@@ -1585,7 +1591,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1594,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>111</v>
@@ -1608,7 +1614,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>112</v>
@@ -1617,10 +1623,10 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1631,19 +1637,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1654,19 +1660,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1677,19 +1683,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1700,7 +1706,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>118</v>
@@ -1709,7 +1715,7 @@
         <v>37</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>119</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>120</v>
@@ -1732,7 +1738,7 @@
         <v>37</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>121</v>
@@ -1746,7 +1752,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>122</v>
@@ -1755,7 +1761,7 @@
         <v>37</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>123</v>
@@ -1769,19 +1775,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1792,16 +1798,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>129</v>
@@ -1815,7 +1821,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>130</v>
@@ -1824,7 +1830,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>131</v>
@@ -1838,7 +1844,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>132</v>
@@ -1847,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>133</v>
@@ -1861,16 +1867,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>135</v>
@@ -1884,16 +1890,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>137</v>
@@ -1907,24 +1913,47 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>18</v>
       </c>
     </row>
